--- a/document/log/grok/session-log.xlsx
+++ b/document/log/grok/session-log.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="SESS" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="84">
   <si>
     <t xml:space="preserve">SESS</t>
   </si>
@@ -42,13 +42,19 @@
     <t xml:space="preserve">Session Title</t>
   </si>
   <si>
+    <t xml:space="preserve">Session Reference</t>
+  </si>
+  <si>
     <t xml:space="preserve">SESS.A</t>
   </si>
   <si>
     <t xml:space="preserve">Session A</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyzing Document Process Manager</t>
+    <t xml:space="preserve">DPM Analysis, Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_e4251ecb-6263-4ce7-9792-15caf434b5b0</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -60,19 +66,16 @@
     <t xml:space="preserve">Session Details</t>
   </si>
   <si>
-    <t xml:space="preserve">Session Reference</t>
-  </si>
-  <si>
     <t xml:space="preserve">Session Account</t>
   </si>
   <si>
+    <t xml:space="preserve">Original Date</t>
+  </si>
+  <si>
     <t xml:space="preserve">DPM Documentation Samples</t>
   </si>
   <si>
     <t xml:space="preserve">Create a sample markdown document file for four different types of files to be created for DPM: API-001, API-002, API-010, API-018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_e4251ecb-6263-4ce7-9792-15caf434b5b0</t>
   </si>
   <si>
     <t xml:space="preserve">recourse-coutility@outlook.com</t>
@@ -133,22 +136,7 @@
 DPM Documentation Outline</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Notice that Core-Plex is a dependency of Document Process Manager. Review Core-Plex documentation at </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">https://github.com/thomaspatrickwelborn/core-plex as well as https://npmjs.com/core-plex. Then notice how Core-Plex API is utilized by Document Process Manager. 
+    <t xml:space="preserve">Notice that Core-Plex is a dependency of Document Process Manager. Review Core-Plex documentation at https://github.com/thomaspatrickwelborn/core-plex as well as https://npmjs.com/core-plex. Then notice how Core-Plex API is utilized by Document Process Manager. 
 The style and structure of documentation should resemble Core-Plex, Recourse, Objecture, and other of my own, original libraries/frameworks. Remember when markdown files are created in the session window they should be copy-pasteable with one click sans all other message data. 
 Documentation Structure: 
 /README.md – Impetus, Introduction, Installation, Instantiation, Implementation, Instructions
@@ -156,7 +144,6 @@
 /document/guide/** – Documentation for practical application (such as usage throughout Core-Plex, Recourse, Objecture, etc). 
 Generally there should be one /api file for all fo the classes in the development class system; there should be guides that separately describe practical application. 
 Before generating documentation, create an outline within a session display table. </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_22b91237-113e-4fdc-8a2e-a50425db6b52</t>
@@ -203,17 +190,149 @@
     <t xml:space="preserve">Session B</t>
   </si>
   <si>
-    <t xml:space="preserve">Reviewing Document Process Manager</t>
+    <t xml:space="preserve">DPM Install Analysis, Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_1b0afed7-42d9-4b91-92ea-75ecea3ee269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation Restart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Installation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now verify that all dependencies and devDependencies from the last output are configured accurately, specifically the existing ones before new added. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation Reconsiderations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now create sample DPM project files with NPM configurations based on this original:
+```
+{
+  "name": "objecture-demonstrament",
+  "version": "1.0.0",
+  "description": "",
+  "license": "ISC",
+  "author": "Thomas Patrick Welborn",
+  "type": "module",
+  "main": "index.js",
+  "scripts": {
+    "start": "pm2 start ecosystem.config.cjs",
+    "restart": "pm2 restart ecosystem.config.cjs",
+    "stop": "pm2 stop ecosystem.config.cjs",
+    "delete": "pm2 delete ecosystem.config.cjs"
+  },
+  "dependencies": {
+    "document-process-manager": "^1.6.0",
+    "recourse": "^1.2.1"
+  },
+  "devDependencies": {
+    "chokidar": "^4.0.3",
+    "nodemon": "^3.1.9"
+  }
+}
+```
+Based on need to install dependencies when the package is installed, which dependencies or devDependencies should be added?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_2631a7ad-40d9-45a8-9cf1-67eb20e05336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now irrespective of herein session describe how to use existing unmodified DPM and DPM instances (from examples) configuration files but ensure installation of all dependencies. Ensure the package.json files are reviewed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_851b4644-7ba8-4468-a8e1-89c62292788d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPM CLI Simplification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider omitting all `bin/index.js` or setup herein. Instead consider allowing `bin/index.js` to remain unmodified from original and only allow updates to ecosystem config and package config. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_c588d7a8-2293-4380-8a28-f11830fd94fb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPM `bin/index.js` File – Clarification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">And now recreate the final bin index file without any ecosystem file creation – this will be created by the user or another process. Instead recreate an example (based on Objecture, Recourse) demonstrament ecosystem config files with separate global/local installation. Also make final consideration that the scripts are invoked within the npm scripts property. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_fd50a944-d30d-4524-be28-250f6643d8ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now reconsider the last output `bin/index.js` File. Notice the code creates an ecosystem configuration file. Is this necessary or can the ecosystem file be created independently. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_199a3c55-cfde-49ba-a5b2-3cb6d952606d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPM Installation – Code Generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is this the only affected file? I am going to assume this works or I am going to assume that I can use enough information from it to make it work myself. If not the only affected file create remaining. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_73867a70-cb73-413b-954b-532a6b3a037c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPM Installation Modes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider all output herein. The last output is the ideal approach and will be referred to as DPM Installation Modes. It should be implemented as described, however all affected development files must be recreated and they must pass logical validation. It is not necessary to generate codebase documentation files yet. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_50f8cd48-1358-48e4-ac9f-a14e7e146c1c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation-Driven Optionality with Dual-Mode Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider documentation-driven optionality with dual-mode support. This is the ideal option because it requires limited maintenance for the project. However it must always adequately allow either a global or local installation. This should be able to achieve using PM2 Ecosystem file with 2 configurations in the same file. If so, then there should be a CLI flag specificying global or local dependency installation. 
+Further consider viability of also optionally allowing DPM global or local installation AND global or local dependency installation. 
+Finally, it should be possible to specify which dependencies to install or not install, or to install all default current. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_f519adee-1442-470d-855a-c3f3473897c2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achieving Optional Global Or Local Installation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider integrating optional global or local installation. This must be an option that would be available through the CLI. Notice through example projects (Recourse, Objecture) demonstrament folders that DPM CLI statements are located `/demonstrament/ecosystem.config.cjs`, that `pm2` `ecosystem.config` file is invoked through adjacent `package.json` `scripts` property, and that adjacent `dpm.config.documents` file is consumed by a new instance of DPM (see bin for code), then further DPM configuration files through simplex-to-complex depth location and specified filenames or filename patterns for varied piler consumption. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_8f7d787a-d90e-44de-b442-e74dc4338d2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achieving Ideal DPM Installation Outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideally a new DPM user will install globally and all dependencies will also install. Describe methods to achieve either this ideal or other ideal outcomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_8b4f713e-3926-4ddc-b9bf-81a30057d189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPM Installation Overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consider the attached session spreadsheet logging grok sessions for DPM. Use `SESS.A` tab specifically to gain initial understanding and information about DPM. 
+The purpose of this session is to analyze and report technical installation overview. Specifically notice that DPM is an NPM package with global installation (contained within `/bin` folder). Notice that DPM dependencies include all of the dependencies required by pilers and other aspects of DPM to perform in a localized development system. Describe technical requirements for this to perform – specifically if all of the DPM dependencies must also be installed in a local project or system folder. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -242,11 +361,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -290,7 +404,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -332,22 +446,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -474,10 +584,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -501,6 +613,9 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="str">
@@ -513,7 +628,11 @@
       </c>
       <c r="C3" s="3" t="str">
         <f aca="false">'SESS.A'!C1</f>
-        <v>Analyzing Document Process Manager</v>
+        <v>DPM Analysis, Review</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f aca="false">'SESS.A'!D1</f>
+        <v>https://grok.com/share/c2hhcmQtNQ_e4251ecb-6263-4ce7-9792-15caf434b5b0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -527,7 +646,11 @@
       </c>
       <c r="C4" s="3" t="str">
         <f aca="false">'SESS.B'!C1</f>
-        <v>Reviewing Document Process Manager</v>
+        <v>DPM Install Analysis, Review</v>
+      </c>
+      <c r="D4" s="3" t="str">
+        <f aca="false">'SESS.B'!D1</f>
+        <v>https://grok.com/share/c2hhcmQtNQ_1b0afed7-42d9-4b91-92ea-75ecea3ee269</v>
       </c>
     </row>
   </sheetData>
@@ -546,279 +669,319 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="4.61"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="29.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="66.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="23.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="71.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="59.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="E1" s="6"/>
       <c r="F1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B3" s="10" t="str">
+      <c r="B3" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A3)</f>
         <v>SESS.A.9</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>14</v>
+      <c r="C3" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" s="12" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B4" s="10" t="str">
+      <c r="B4" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A4)</f>
         <v>SESS.A.8</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>18</v>
+      <c r="C4" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="E4" s="10" t="s">
+        <v>21</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B5" s="10" t="str">
+      <c r="B5" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A5)</f>
         <v>SESS.A.8</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>23</v>
       </c>
+      <c r="E5" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" s="12" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B6" s="10" t="str">
+      <c r="B6" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A6)</f>
         <v>SESS.A.7</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>24</v>
+      <c r="C6" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="11" t="s">
         <v>26</v>
       </c>
+      <c r="E6" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>45349</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="str">
+      <c r="B7" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A7)</f>
         <v>SESS.A.6</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>26</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>45349</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="str">
+      <c r="B8" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A8)</f>
         <v>SESS.A.5</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>29</v>
+      <c r="C8" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="11" t="s">
         <v>31</v>
       </c>
+      <c r="E8" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="F8" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="str">
+      <c r="B9" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A9)</f>
         <v>SESS.A.4</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>32</v>
+      <c r="C9" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="11" t="s">
         <v>34</v>
       </c>
+      <c r="E9" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="F9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>45349</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="10" t="str">
+      <c r="B10" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A10)</f>
         <v>SESS.A.3</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>35</v>
+      <c r="C10" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>45349</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="10" t="str">
+      <c r="B11" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A11)</f>
         <v>SESS.A.2</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>37</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>45349</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="258.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="10" t="str">
+      <c r="B12" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A12)</f>
         <v>SESS.A.1</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>42</v>
       </c>
+      <c r="E12" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="F12" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="337.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="B13" s="10" t="str">
+      <c r="B13" s="7" t="str">
         <f aca="false">_xlfn.CONCAT($A$1, ".", $A13)</f>
         <v>SESS.A.0</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>45</v>
       </c>
+      <c r="E13" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="F13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>45349</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -845,67 +1008,368 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="4.61"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="29.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="57.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="23.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="71.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.98"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="C1" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="F1" s="6"/>
-      <c r="G1" s="11"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A3)</f>
+        <v>SESS.B.11</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A4)</f>
+        <v>SESS.B.11</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="348.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="n">
+      <c r="B5" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A5)</f>
+        <v>SESS.B.10</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A6)</f>
+        <v>SESS.B.9</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A7)</f>
+        <v>SESS.B.8</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A8)</f>
+        <v>SESS.B.7</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A9)</f>
+        <v>SESS.B.6</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A10)</f>
+        <v>SESS.B.5</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A11)</f>
+        <v>SESS.B.4</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A12)</f>
+        <v>SESS.B.3</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A13)</f>
+        <v>SESS.B.2</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A14)</f>
+        <v>SESS.B.1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="str">
-        <f aca="false">_xlfn.CONCAT($A$1, ".", $A3)</f>
+      <c r="B15" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A15)</f>
         <v>SESS.B.0</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="C15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/document/log/grok/session-log.xlsx
+++ b/document/log/grok/session-log.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="SESS" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="SESS.A" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="SESS.B" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="SESS.C" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="130">
   <si>
     <t xml:space="preserve">SESS</t>
   </si>
@@ -322,6 +323,310 @@
   <si>
     <t xml:space="preserve">Consider the attached session spreadsheet logging grok sessions for DPM. Use `SESS.A` tab specifically to gain initial understanding and information about DPM. 
 The purpose of this session is to analyze and report technical installation overview. Specifically notice that DPM is an NPM package with global installation (contained within `/bin` folder). Notice that DPM dependencies include all of the dependencies required by pilers and other aspects of DPM to perform in a localized development system. Describe technical requirements for this to perform – specifically if all of the DPM dependencies must also be installed in a local project or system folder. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SESS.C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPM Process – Codebase-Database (CB-DB) Piler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_07cedd95-dc38-47e5-9662-022061b112e3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic AST Table Reformat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider the following proposed table: 
+```tsv
+VERS	Script Ledger	Static 3-column programmatic language ledger													
+SEXTER				LEXTER						DEXTER					
+RID	VERSID	LEX	DEX	SID	BID	CLO	SER	TEN	PER	CLO	SER	TEN	PER	SID	BID
+0	VERS.0	0,0	0,0	0	0		class	EJSPiler			extends	Piler		0	0
+1	VERS.1	1,0	1,0	1	0	{}		#model						1	0
+2	VERS.2	1,1	1,1	1	1			#renderFileOptions						1	1
+3	VERS.3	1,2	1,2	1	2			#compileOptions						1	2
+4	VERS.4	1,3	1,3	1	3			#_root						1	3
+5	VERS.5	1,4	2,0	1	4		constructor			()		$settings	,	2	0
+6	VERS.6	2,1	2,1	2	1							$options	,	2	1
+7	VERS.7	2,2	2,2	2	2							$document		2	2
+8	VERS.8	2,0	3,0	2	0	{}	super			()		...arguments		3	0
+9	VERS.9	1,2	3,0	1	2		get	outputType		()				3	0
+10	VERS.10	2,0	2,0	2	0	{}	return	this.settings.outputType						2	0
+11	VERS.11	1,3	2,0	1	3		get	model		()				2	0
+12	VERS.12	2,0	3,0	2	0	{}	if			()				3	0
+13	VERS.13	3,0	3,1	3	0			this.#model	!==			undefined		3	1
+14	VERS.14	3,0	3,0	3	0	{}	return	this.#model						3	0
+15	VERS.15	2,0	2,0	2	0			this.#model	=			path.join		2	0
+16	VERS.16	3,0	3,0	3	0	()		this.document.source	,					3	0
+17	VERS.17	3,1	3,1	3	1			this.settings.model						3	1
+18	VERS.18	3,2	3,2	3	2		return	this.#model						3	2
+```
+SEXTER - Ledger scope/block location
+LEXTER - Left Statement
+DEXTER - Right Statement
+RID - Row ID (used for tracking rows, appending to VERSID)
+VERSID - "Verse" ID
+SID - Scope ID
+BID - BLock ID
+SER - Reserved keywords
+TEN - Property keys and property values
+PER - Operators, separators, other symbols
+CLO - Closure Symbols Only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_e980701c-801a-476b-8751-b9a39b029798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">document-process-manager@outlook.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider the more sophisticated table representation of a partial JS file. This same structure will also be used to capture CSS and HTML file data. Now consider attached file of original JS. Using the table format and struture below, recreate the file within this table system. 
+```tsv
+SEXTER		LEXTER						DEXTER					
+LEX	DEX	SID	BID	CLO	SER	TEN	PER	CLO	SER	TEN	PER	SID	BID
+0,0	0,0	0	0		class	EJSPiler			extends	Piler		0	0
+1,0	1,0	1	0	{}		#model #renderFileOptions #compileOptions #_root						1	0
+1,1	2,0	1	1		constructor			()		$settings, $options, $document		2	0
+2,0	3,0	2	0	{}	super			()		...arguments		3	0
+1,2	3,0	1	2		get	outputType		()				3	0
+2,0	2,0	2	0	{}	return	this.settings.outputType						2	0
+1,3	2,0	1	3		get	model		()				2	0
+2,0	3,0	2	0	{}	if			()				3	0
+```
+When recreating the table omit import and export statements. Instead use class as the starting point. Import/Export concerns will be managed separately with more information later. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic AST Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider the following table corrections: 
+- There are two header rows. 
+- There is no "Scope" column. 
+- Block ID (BID) is an integer order of blocks within a scope
+- Scope ID (SID) is an integer order of depth subblocks/subscopes. 
+- CLO (Closure) may be the start/stop closure symbols. 
+- SER (Reserved) intended for reserved words. 
+- TEN (Content) intended for property key/property value depending on lexter/dexter
+- PER (Operator/Separator) - Obvious. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_684168e8-8d70-4dab-b6d2-00644f65bb3a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recreate Tree-Sitter AST Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now recreate the previously provided javascript file example within the updated table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_9868902e-f464-42ef-824b-357a59d8166e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spreadsheet Example Clarification #3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider the following shortened version of the previous output table. 
+```tsv
+Scope		Lexter				Dexter			
+BID	SID	CLO	SER	TEN	PER	CLO	SER	TEN	PER
+```
+```
+BID - Block Identifier
+SID - Scope Identifier
+CLO - Closure
+SER - Reserved Word
+TEN - Content
+PER - Operator, Separator
+```</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_bf06d553-c9fc-413a-96df-72cd2a7670bf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spreadsheet Example Clarification #2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a two-row header with properties split between lexter/dexter when possible. There should be two main columns for lexter/dexter. The columns should be readable as if authoring code within them. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_594b1c70-ce2e-45b7-8058-192b23a30e5b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spreadsheet Example Clarification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sample table should be output in tsv format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_878b9052-d943-4cde-90b1-2654e7c72f9b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spreadsheet Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a sample spreadsheet table with the lexter/dexter columns and sub columns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_f045e227-20c3-4cbc-81c4-4c4f05bef15f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Sitter, Mongoose Considerations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Translating a codebase to a database in Mongoose is expected to repeatedly update the same models or expected to constantly delete/create models. 
+Additionally, all properties must be presentable within an interfacile envoironment where codebase AST is authored in a 2-column (sttemented lexter, dexter) with similar/same subcolumns to capture reserved words, operators, variable keys, values, etc. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_33e62e78-f9df-41fb-a35b-37ea375201e2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Sitter Parsement Data Modeling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Sitter parsement is expected to be same object properties with recursion. Create a Mongoose Schema with entire Tree-Sitter parsement for any file (not just JS). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_d47c668d-7299-4055-8978-2fd03140c57e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Sitter Demonstration Clarification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Sitter may be a viable alternative for my original AST. Create a table that describes relevant documentation for Tree-Sitter from output herein session. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_41ee234e-884e-4a9c-abf2-be2d283b5360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Sitter Demonstration JSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider the output tree-sitter AST. Display the output as a JSON file. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_92b92f3d-afbf-4a84-9694-24ef9c589485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Sitter Demonstration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider the following sample JS file. Transform the JS file to tree-sitter AST: 
+```
+import Core from '../../core/index.js'
+import path from 'node:path'
+import watch from 'glob-watcher'
+export default class Adpiler extends Core {
+  document
+  #active = false
+  #input
+  #output
+  #watch
+  #ignore
+  #watcher
+  constructor($settings, $options, $document) {
+    super(...arguments)
+    this.document = $document
+    this.addEvents([
+      // Watcher Events
+      {
+        path: 'watcher', type: 'add',
+        listener: this.pile,
+        assign: 'on', deassign: 'off',
+      },
+      {
+        path: 'watcher', type: 'change',
+        listener: this.pile,
+        assign: 'on', deassign: 'off',
+      }
+    ])
+    Object.defineProperties(this, {
+      watcher: {
+        enumerable: true,
+        get() {
+          if(
+            this.#watcher !== undefined || 
+            this.watch === undefined
+          ) { return this.#watcher }
+          let watcher = watch(this.watch, {
+            ignored: this.ignore,
+            ignoreInitial: false,
+            awaitWriteFinish: true,
+          })
+          this.#watcher = watcher
+          this.enableEvents({ path: 'watcher' })
+          return this.#watcher
+        }
+      }
+    })
+    this.watcher
+    this.enableEvents()
+  }
+  get active() { return this.#active }
+  set active($active) {
+    if(this.#active === $active) { return }
+    if(this.watcher !== undefined) {
+      if($active === true) {
+        this.watcher
+      }
+      else if($active === false) {
+        this.watcher.close()
+        this.#watcher = undefined
+      }
+    }
+    this.#active = $active
+  }
+  get type() { return this.settings.type }
+  get input() {
+    if(this.#input !== undefined) { return this.#input }
+    this.#input = path.join(this.document.source, this.settings.input)
+    return this.#input
+  }
+  get output() {
+    if(this.#output !== undefined) { return this.#output }
+    this.#output = path.join(this.document.target, this.settings.output)
+    return this.#output
+  }
+  get watch() {
+    if(this.#watch !== undefined) { return this.#watch }
+    if(!this.settings.watch) { return this.#watch }
+    const watch = this.settings.watch.map(
+      ($watchPath) =&gt; path.join(this.document.source, $watchPath)
+    )
+    if(watch.length) { this.#watch = watch }
+    return this.#watch
+  }
+  get ignore() {
+    if(this.#ignore !== undefined) { return this.#ignore }
+    this.#ignore = Array.prototype.concat(
+      this.settings.ignore.map(
+        ($ignorePath) =&gt; path.join(this.document.source, $ignorePath)
+      ),
+      this.document.ignore
+    )
+    return this.#ignore
+  }
+}
+```</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtNQ_80ada8e8-a5a1-4b1c-ac8e-8db6d8bd0f4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tree-Sitter Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describe how tree-sitter may be a viable alternative for a custom solution. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CB-DB Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document Process Manager document generator templates consume document models describing some document structure. DPM's initial primary focus is web document systems and most document models, document templates are created for this purpose. There is a default document model with definitive property structure and autorecursion that is capable of rendering programmatic language files universally. This is achieved by separating syntax, symbols, and content used in programmatic languages into distinct properties with reductive name (greek/latin roots) describing separated part's purpose. Programmatic languages are comprised of blocks -&gt; statements -&gt; expressions that are further comprised of reserved words, closures, comparators, etc. A univeral generic programmatic language file (JS, CSS, HTML, MD, PHP, PY, etc.) should share a set of minimalistic properties containing different classifications of syntax. Alternately, a programmatic language document should be transformable to a default universal abstract syntax tree as described herein. 
+This is a process that I already achieved during prior development on experimental projects. Ability to process documents with default universal programmatic language files is essential for Document Process Manager. </t>
   </si>
 </sst>
 </file>
@@ -584,7 +889,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.14"/>
@@ -652,6 +957,25 @@
         <f aca="false">'SESS.B'!D1</f>
         <v>https://grok.com/share/c2hhcmQtNQ_1b0afed7-42d9-4b91-92ea-75ecea3ee269</v>
       </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="str">
+        <f aca="false">'SESS.C'!A1</f>
+        <v>SESS.C</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f aca="false">'SESS.C'!B1</f>
+        <v>Session C</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <f aca="false">'SESS.C'!C1</f>
+        <v>DPM Process – Codebase-Database (CB-DB) Piler</v>
+      </c>
+      <c r="D5" s="3" t="str">
+        <f aca="false">'SESS.C'!D1</f>
+        <v>https://grok.com/share/c2hhcmQtNQ_07cedd95-dc38-47e5-9662-022061b112e3</v>
+      </c>
+      <c r="E5" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -741,7 +1065,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -765,7 +1089,7 @@
         <v>18</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -789,7 +1113,7 @@
         <v>18</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -813,7 +1137,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -837,7 +1161,7 @@
         <v>18</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -861,7 +1185,7 @@
         <v>18</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -885,7 +1209,7 @@
         <v>18</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -909,7 +1233,7 @@
         <v>18</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -933,7 +1257,7 @@
         <v>18</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="258.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -957,7 +1281,7 @@
         <v>18</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -981,7 +1305,7 @@
         <v>18</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>45349</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1075,7 +1399,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1099,7 +1423,7 @@
         <v>18</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="348.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1123,7 +1447,7 @@
         <v>18</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1147,7 +1471,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1171,7 +1495,7 @@
         <v>18</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1195,7 +1519,7 @@
         <v>18</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1219,7 +1543,7 @@
         <v>18</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1243,7 +1567,7 @@
         <v>18</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1267,7 +1591,7 @@
         <v>18</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1291,7 +1615,7 @@
         <v>18</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1315,7 +1639,7 @@
         <v>18</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1339,7 +1663,7 @@
         <v>18</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1363,7 +1687,7 @@
         <v>18</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>45350</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1371,6 +1695,522 @@
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.95" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="9.21"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="71.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.21"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A3)</f>
+        <v>SESS.C.14</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A4)</f>
+        <v>SESS.C.13</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A5)</f>
+        <v>SESS.C.12</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B6" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A6)</f>
+        <v>SESS.C.11</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A7)</f>
+        <v>SESS.C.10</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A8)</f>
+        <v>SESS.C.9</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A9)</f>
+        <v>SESS.C.8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A10)</f>
+        <v>SESS.C.7</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A11)</f>
+        <v>SESS.C.6</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A12)</f>
+        <v>SESS.C.5</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A13)</f>
+        <v>SESS.C.4</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A14)</f>
+        <v>SESS.C.3</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A15)</f>
+        <v>SESS.C.2</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A16)</f>
+        <v>SESS.C.1</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" s="7" t="str">
+        <f aca="false">_xlfn.CONCAT($A$1, ".", $A17)</f>
+        <v>SESS.C.0</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="10"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" s="1" customFormat="true" ht="12.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
